--- a/Configs/GameConfig/Datas/fg/#StatusTag-状态标签.xlsx
+++ b/Configs/GameConfig/Datas/fg/#StatusTag-状态标签.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,21 @@
           <t>kind</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>bit</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>effect</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -489,6 +504,21 @@
           <t>string</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -524,6 +554,21 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>status=状态标签(单位头顶显示,FGR-FW-031);marker=机制标记(旧引擎模块给能量包打的行为记号,只给反应判定/伤害归因/调试用,不在头顶显示)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>战斗内核状态位 0～30(31 保留给区域减速);同义标签与主标签相同;机制标记 -1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>内核效果:none/dot/slow/vuln/leech/execute(dot=每秒伤害,slow=减速比例,vuln=易伤比例,leech=回收修复比例,execute=处决阈值,none=只是反应用的标签)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>效果数值(见 effect)</t>
         </is>
       </c>
     </row>
@@ -559,6 +604,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -592,6 +648,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -625,6 +692,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -658,6 +736,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>vuln</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -691,6 +780,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>vuln</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -724,6 +824,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>slow</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -757,6 +868,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H10" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -790,6 +912,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H11" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -823,6 +956,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -856,6 +1000,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H13" t="n">
+        <v>9</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>leech</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -889,6 +1044,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>execute</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -922,6 +1088,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H15" t="n">
+        <v>11</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -955,6 +1132,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -988,6 +1176,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H17" t="n">
+        <v>13</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -1021,6 +1220,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H18" t="n">
+        <v>14</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>slow</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -1054,6 +1264,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H19" t="n">
+        <v>15</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -1087,6 +1308,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H20" t="n">
+        <v>16</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -1120,6 +1352,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H21" t="n">
+        <v>17</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -1153,6 +1396,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H22" t="n">
+        <v>18</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
@@ -1186,6 +1440,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H23" t="n">
+        <v>19</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
@@ -1219,6 +1484,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H24" t="n">
+        <v>20</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
@@ -1252,6 +1528,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H25" t="n">
+        <v>21</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -1285,6 +1572,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H26" t="n">
+        <v>22</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -1318,6 +1616,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H27" t="n">
+        <v>23</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -1351,6 +1660,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H28" t="n">
+        <v>24</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
@@ -1384,6 +1704,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H29" t="n">
+        <v>25</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
@@ -1417,6 +1748,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
@@ -1450,6 +1792,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -1483,6 +1836,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H32" t="n">
+        <v>4</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>vuln</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
@@ -1516,6 +1880,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H33" t="n">
+        <v>10</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>execute</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
@@ -1549,6 +1924,17 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H34" t="n">
+        <v>11</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
@@ -1582,6 +1968,17 @@
           <t>marker</t>
         </is>
       </c>
+      <c r="H35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
@@ -1615,6 +2012,17 @@
           <t>marker</t>
         </is>
       </c>
+      <c r="H36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
@@ -1648,6 +2056,17 @@
           <t>marker</t>
         </is>
       </c>
+      <c r="H37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
@@ -1681,6 +2100,17 @@
           <t>marker</t>
         </is>
       </c>
+      <c r="H38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
@@ -1714,6 +2144,17 @@
           <t>marker</t>
         </is>
       </c>
+      <c r="H39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
@@ -1747,6 +2188,17 @@
           <t>marker</t>
         </is>
       </c>
+      <c r="H40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
@@ -1780,6 +2232,17 @@
           <t>marker</t>
         </is>
       </c>
+      <c r="H41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
@@ -1813,6 +2276,17 @@
           <t>marker</t>
         </is>
       </c>
+      <c r="H42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
@@ -1846,6 +2320,17 @@
           <t>marker</t>
         </is>
       </c>
+      <c r="H43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
@@ -1879,6 +2364,17 @@
           <t>marker</t>
         </is>
       </c>
+      <c r="H44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
@@ -1912,6 +2408,17 @@
           <t>marker</t>
         </is>
       </c>
+      <c r="H45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
@@ -1945,6 +2452,17 @@
           <t>marker</t>
         </is>
       </c>
+      <c r="H46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
@@ -1978,6 +2496,17 @@
           <t>marker</t>
         </is>
       </c>
+      <c r="H47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
@@ -2011,6 +2540,17 @@
           <t>marker</t>
         </is>
       </c>
+      <c r="H48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
@@ -2043,6 +2583,17 @@
         <is>
           <t>marker</t>
         </is>
+      </c>
+      <c r="H49" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#StatusTag-状态标签.xlsx
+++ b/Configs/GameConfig/Datas/fg/#StatusTag-状态标签.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2116,12 +2116,12 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FeedbackHit</t>
+          <t>Woven</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>tag.feedbackhit.name</t>
+          <t>tag.woven.name</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2160,12 +2160,12 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Woven</t>
+          <t>Orbiting</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>tag.woven.name</t>
+          <t>tag.orbiting.name</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2204,12 +2204,12 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Orbiting</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>tag.orbiting.name</t>
+          <t>tag.rippling.name</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2248,12 +2248,12 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Valved</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>tag.rippling.name</t>
+          <t>tag.valved.name</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2292,12 +2292,12 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Valved</t>
+          <t>Thorns</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>tag.valved.name</t>
+          <t>tag.thorns.name</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2336,12 +2336,12 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Thorns</t>
+          <t>Overheat</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>tag.thorns.name</t>
+          <t>tag.overheat.name</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2380,12 +2380,12 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Overheat</t>
+          <t>Merged</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>tag.overheat.name</t>
+          <t>tag.merged.name</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2424,12 +2424,12 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Merged</t>
+          <t>Insulated</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>tag.merged.name</t>
+          <t>tag.insulated.name</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2468,12 +2468,12 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Insulated</t>
+          <t>FuseTripped</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>tag.insulated.name</t>
+          <t>tag.fusetripped.name</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2512,12 +2512,12 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FuseTripped</t>
+          <t>Filtered</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>tag.fusetripped.name</t>
+          <t>tag.filtered.name</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2549,50 +2549,6 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Filtered</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>tag.filtered.name</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>marker</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
         <v>0</v>
       </c>
     </row>
